--- a/res/vuz/leti.xlsx
+++ b/res/vuz/leti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D33139-C9ED-43F9-B59C-98B4AB259F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72751E7B-2814-41FA-91ED-24A9650353AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="216">
   <si>
     <t>#name</t>
   </si>
@@ -607,9 +607,6 @@
   </si>
   <si>
     <t>химико-биотехнологический</t>
-  </si>
-  <si>
-    <t>1 2 3 4 5 6 14 15 17 18 19 20</t>
   </si>
   <si>
     <t>MI</t>
@@ -1029,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -2086,7 +2083,7 @@
         <v>42</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>41</v>
@@ -2106,7 +2103,7 @@
         <v>42</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>65</v>
@@ -2126,7 +2123,7 @@
         <v>42</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>37</v>
@@ -2146,10 +2143,10 @@
         <v>42</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2166,10 +2163,10 @@
         <v>42</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2186,10 +2183,10 @@
         <v>42</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2206,7 +2203,7 @@
         <v>42</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>37</v>
@@ -2226,7 +2223,7 @@
         <v>42</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>65</v>
@@ -2246,7 +2243,7 @@
         <v>42</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>65</v>
@@ -2266,10 +2263,10 @@
         <v>42</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2286,10 +2283,10 @@
         <v>42</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2306,10 +2303,10 @@
         <v>42</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2326,10 +2323,10 @@
         <v>42</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2346,7 +2343,7 @@
         <v>42</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>41</v>
@@ -2366,10 +2363,10 @@
         <v>42</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2386,10 +2383,10 @@
         <v>42</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2406,10 +2403,10 @@
         <v>42</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2426,10 +2423,10 @@
         <v>42</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2446,10 +2443,10 @@
         <v>42</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2466,10 +2463,10 @@
         <v>42</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2486,10 +2483,10 @@
         <v>42</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2506,10 +2503,10 @@
         <v>42</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2526,10 +2523,10 @@
         <v>42</v>
       </c>
       <c r="E76" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2546,10 +2543,10 @@
         <v>42</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2566,10 +2563,10 @@
         <v>42</v>
       </c>
       <c r="E78" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2586,10 +2583,10 @@
         <v>42</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2606,7 +2603,7 @@
         <v>42</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>65</v>
@@ -2626,7 +2623,7 @@
         <v>42</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>37</v>
@@ -2646,10 +2643,10 @@
         <v>42</v>
       </c>
       <c r="E82" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2666,10 +2663,10 @@
         <v>42</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2686,10 +2683,10 @@
         <v>42</v>
       </c>
       <c r="E84" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2706,10 +2703,10 @@
         <v>42</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2726,7 +2723,7 @@
         <v>42</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>65</v>
@@ -2746,10 +2743,10 @@
         <v>42</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2766,7 +2763,7 @@
         <v>42</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>37</v>
@@ -2786,7 +2783,7 @@
         <v>42</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>37</v>
@@ -2806,10 +2803,10 @@
         <v>42</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2826,10 +2823,10 @@
         <v>42</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -2846,10 +2843,10 @@
         <v>42</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2866,7 +2863,7 @@
         <v>42</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>37</v>
@@ -2886,10 +2883,10 @@
         <v>42</v>
       </c>
       <c r="E94" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -2906,10 +2903,10 @@
         <v>42</v>
       </c>
       <c r="E95" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -2926,10 +2923,10 @@
         <v>42</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -2946,10 +2943,10 @@
         <v>42</v>
       </c>
       <c r="E97" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -2966,10 +2963,10 @@
         <v>42</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -2986,10 +2983,10 @@
         <v>42</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3006,10 +3003,10 @@
         <v>42</v>
       </c>
       <c r="E100" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3026,10 +3023,10 @@
         <v>42</v>
       </c>
       <c r="E101" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3046,10 +3043,10 @@
         <v>42</v>
       </c>
       <c r="E102" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3066,7 +3063,7 @@
         <v>42</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>37</v>
@@ -3086,10 +3083,10 @@
         <v>42</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3106,10 +3103,10 @@
         <v>42</v>
       </c>
       <c r="E105" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3126,10 +3123,10 @@
         <v>42</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3146,10 +3143,10 @@
         <v>42</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3166,7 +3163,7 @@
         <v>42</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>65</v>
@@ -3186,10 +3183,10 @@
         <v>42</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3206,10 +3203,10 @@
         <v>42</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3226,10 +3223,10 @@
         <v>42</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3329,7 +3326,7 @@
         <v>163</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3349,7 +3346,7 @@
         <v>163</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3369,7 +3366,7 @@
         <v>163</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3449,7 +3446,7 @@
         <v>163</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3469,7 +3466,7 @@
         <v>163</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3489,7 +3486,7 @@
         <v>163</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3509,7 +3506,7 @@
         <v>163</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3549,7 +3546,7 @@
         <v>163</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3589,7 +3586,7 @@
         <v>163</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3609,7 +3606,7 @@
         <v>163</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3649,7 +3646,7 @@
         <v>163</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -3669,7 +3666,7 @@
         <v>163</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -3689,7 +3686,7 @@
         <v>163</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3709,7 +3706,7 @@
         <v>163</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -3729,7 +3726,7 @@
         <v>163</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -3749,7 +3746,7 @@
         <v>163</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -3769,7 +3766,7 @@
         <v>163</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -3789,7 +3786,7 @@
         <v>163</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -3809,7 +3806,7 @@
         <v>163</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -3829,7 +3826,7 @@
         <v>163</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -3869,7 +3866,7 @@
         <v>163</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -3889,7 +3886,7 @@
         <v>163</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -3909,7 +3906,7 @@
         <v>163</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -3929,7 +3926,7 @@
         <v>163</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -3949,7 +3946,7 @@
         <v>163</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -3969,7 +3966,7 @@
         <v>163</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4009,7 +4006,7 @@
         <v>163</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4029,7 +4026,7 @@
         <v>163</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4049,7 +4046,7 @@
         <v>163</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4069,7 +4066,7 @@
         <v>163</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4109,7 +4106,7 @@
         <v>163</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4129,7 +4126,7 @@
         <v>163</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4149,7 +4146,7 @@
         <v>163</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4169,7 +4166,7 @@
         <v>163</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4189,7 +4186,7 @@
         <v>163</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4209,7 +4206,7 @@
         <v>163</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4229,7 +4226,7 @@
         <v>163</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4249,7 +4246,7 @@
         <v>163</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4269,7 +4266,7 @@
         <v>163</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4309,7 +4306,7 @@
         <v>163</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4349,7 +4346,7 @@
         <v>163</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4369,7 +4366,7 @@
         <v>163</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4389,7 +4386,7 @@
         <v>163</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -4409,7 +4406,7 @@
         <v>163</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -4429,7 +4426,7 @@
         <v>163</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -4449,7 +4446,7 @@
         <v>163</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -4469,7 +4466,7 @@
         <v>166</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -4529,7 +4526,7 @@
         <v>166</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -4649,7 +4646,7 @@
         <v>166</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -4729,7 +4726,7 @@
         <v>166</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -4749,7 +4746,7 @@
         <v>166</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -4769,7 +4766,7 @@
         <v>166</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -4789,7 +4786,7 @@
         <v>166</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -4829,7 +4826,7 @@
         <v>166</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -4849,7 +4846,7 @@
         <v>166</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -4869,7 +4866,7 @@
         <v>166</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -4889,7 +4886,7 @@
         <v>166</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -4909,7 +4906,7 @@
         <v>166</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -4929,7 +4926,7 @@
         <v>166</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -4969,7 +4966,7 @@
         <v>166</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5029,7 +5026,7 @@
         <v>166</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5100,7 +5097,7 @@
         <v>44</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>42</v>
@@ -5209,7 +5206,7 @@
         <v>166</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -5229,7 +5226,7 @@
         <v>166</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -5269,7 +5266,7 @@
         <v>166</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -5329,7 +5326,7 @@
         <v>166</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -5349,7 +5346,7 @@
         <v>166</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -5369,7 +5366,7 @@
         <v>166</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -5400,7 +5397,7 @@
         <v>44</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>42</v>
@@ -5429,7 +5426,7 @@
         <v>166</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -5449,7 +5446,7 @@
         <v>166</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -5589,7 +5586,7 @@
         <v>91</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -5629,7 +5626,7 @@
         <v>91</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -5640,7 +5637,7 @@
         <v>44</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>42</v>
@@ -5649,7 +5646,7 @@
         <v>91</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -5669,7 +5666,7 @@
         <v>91</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -5680,7 +5677,7 @@
         <v>44</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>42</v>
@@ -5689,7 +5686,7 @@
         <v>91</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -5700,7 +5697,7 @@
         <v>44</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>42</v>
@@ -5720,7 +5717,7 @@
         <v>44</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>42</v>
@@ -5760,7 +5757,7 @@
         <v>44</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>42</v>
@@ -5789,7 +5786,7 @@
         <v>91</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -5820,7 +5817,7 @@
         <v>44</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>42</v>
@@ -5829,7 +5826,7 @@
         <v>91</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -5840,7 +5837,7 @@
         <v>44</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>42</v>
